--- a/stories/arbres/ATOM-JEU.REG.001-01.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kenzo et papa jouent aux cartes, à la table. Les cartes sont lisses. Kenzo a envie de gagner. Papa pose sa dernière carte. Papa a gagné. Kenzo sent un nœud dans le ventre. Ses yeux piquent un peu. Papa dit : l'autre peut gagner. C'est le jeu. Kenzo dit : je suis déçu. Papa dit : être déçu, c'est permis. Kenzo souffle. Il dit : bravo papa. Papa sourit. Kenzo range une carte. Papa dit : on peut rejouer plus tard. Kenzo hoche la tête. Il va boire de l'eau. Le nœud se desserre. Perdre, c'est le jeu. On peut être déçu. On dit bravo. On rejoue plus tard.</t>
+          <t>Kenzo et papa jouent aux cartes, à la table. Les cartes sont lisses. Kenzo a envie de gagner. Papa pose sa dernière carte. Papa a gagné. Kenzo sent un nœud dans le ventre. Ses yeux piquent un peu. L'autre peut gagner. C'est le jeu. Je suis déçu. Être déçu, c'est permis. Kenzo souffle. Bravo papa. Papa sourit. Kenzo range une carte. On peut rejouer plus tard. Kenzo hoche la tête. Il va boire de l'eau. Le nœud se desserre. Perdre, c'est le jeu. On peut être déçu. On dit bravo. On rejoue plus tard.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo et papa jouent aux cartes, à la table. Les cartes sont lisses. Kenzo a envie de gagner. Papa pose sa dernière carte. Papa a gagné. Kenzo sent un nœud dans le ventre. Ses yeux piquent un peu.
+papa|L'autre peut gagner. C'est le jeu.
+enfant-m|Je suis déçu.
+papa|Être déçu, c'est permis.
+narrateur|Kenzo souffle.
+narrateur|Bravo papa. Papa sourit.
+narrateur|Kenzo range une carte.
+papa|On peut rejouer plus tard.
+narrateur|Kenzo hoche la tête. Il va boire de l'eau. Le nœud se desserre. Perdre, c'est le jeu. On peut être déçu. On dit bravo. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Papa a gagné. Que peut faire Kenzo ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a dit bravo. Il était déçu, et c'était permis. Ils rejoueront plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo range la boîte. Papa range la nappe. Ils vont lire un livre.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.001-01.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,7 @@
 narrateur|Kenzo hoche la tête. Il va boire de l'eau. Le nœud se desserre. Perdre, c'est le jeu. On peut être déçu. On dit bravo. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Papa a gagné. Que peut faire Kenzo ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Kenzo a dit bravo. Il était déçu, et c'était permis. Ils rejoueront plus tard.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Kenzo range la boîte. Papa range la nappe. Ils vont lire un livre.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.REG.001-01.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kenzo dit bravo</t>
+          <t>Le cacao et les cartes d'Amir</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sous la vapeur du cacao, Amir perd aux cartes. Il nomme sa déception, dit bravo, et ils rejoueront plus tard.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kenzo et papa jouent aux cartes, à la table. Les cartes sont lisses. Kenzo a envie de gagner. Papa pose sa dernière carte. Papa a gagné. Kenzo sent un nœud dans le ventre. Ses yeux piquent un peu. L'autre peut gagner. C'est le jeu. Je suis déçu. Être déçu, c'est permis. Kenzo souffle. Bravo papa. Papa sourit. Kenzo range une carte. On peut rejouer plus tard. Kenzo hoche la tête. Il va boire de l'eau. Le nœud se desserre. Perdre, c'est le jeu. On peut être déçu. On dit bravo. On rejoue plus tard.</t>
+          <t>La pendule de bois fait tic, tout doux. Un peu de vapeur monte du cacao. Elle laisse un rond sur la vitre. La nappe à carreaux est un peu rêche. Une boîte de cartes dépasse du tiroir. Tu as vu le rond sur la vitre, Amir ? Oui, papa. C'est chaud. En ce moment, papa ouvre la boîte. Les cartes sont lisses et un peu froides. Amir les pose sur la nappe, une par une. Elles sentent le bois. Oui. On joue un petit tour. Amir a envie de gagner. Il regarde ses cartes, tout près. Papa pose sa dernière carte. J'ai fini. J'ai gagné ce tour. Amir sent un nœud dans le ventre. Ses yeux piquent un peu. Je suis déçu. Être déçu, c'est permis. L'autre peut gagner. C'est le jeu. Amir souffle, tout doucement. Le cacao sent encore, tout chaud. Bravo papa. Merci, Amir. Tu as dit bravo. On peut rejouer plus tard. Plus tard ? Oui. D'abord on range un peu. Amir glisse une carte dans la boîte. Le carton fait un petit bruit. Tu as fini de ranger cette carte ? Oui. J'ai encore le nœud. C'est permis. On va boire le cacao. Amir boit une gorgée. C'est doux. Le nœud se desserre un peu. Perdre, c'est le jeu. On peut être déçu. On dit bravo. On rejoue plus tard. On rejoue plus tard. La pendule fait encore tic. Le rond de vapeur s'efface doucement. Tu as dit bravo, Amir. Bravo. Tu as fait du bon travail. L'autre peut gagner. Oui. Et c'est permis d'être déçu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1324,53 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo et papa jouent aux cartes, à la table. Les cartes sont lisses. Kenzo a envie de gagner. Papa pose sa dernière carte. Papa a gagné. Kenzo sent un nœud dans le ventre. Ses yeux piquent un peu.
-papa|L'autre peut gagner. C'est le jeu.
+          <t>narrateur|La pendule de bois fait tic, tout doux.
+narrateur|Un peu de vapeur monte du cacao.
+narrateur|Elle laisse un rond sur la vitre.
+narrateur|La nappe à carreaux est un peu rêche.
+narrateur|Une boîte de cartes dépasse du tiroir.
+papa|Tu as vu le rond sur la vitre, Amir ?
+enfant-m|Oui, papa. C'est chaud.
+narrateur|En ce moment, papa ouvre la boîte.
+narrateur|Les cartes sont lisses et un peu froides.
+narrateur|Amir les pose sur la nappe, une par une.
+enfant-m|Elles sentent le bois.
+papa|Oui. On joue un petit tour.
+narrateur|Amir a envie de gagner.
+narrateur|Il regarde ses cartes, tout près.
+narrateur|Papa pose sa dernière carte.
+papa|J'ai fini. J'ai gagné ce tour.
+narrateur|Amir sent un nœud dans le ventre.
+narrateur|Ses yeux piquent un peu.
 enfant-m|Je suis déçu.
 papa|Être déçu, c'est permis.
-narrateur|Kenzo souffle.
-narrateur|Bravo papa. Papa sourit.
-narrateur|Kenzo range une carte.
+papa|L'autre peut gagner. C'est le jeu.
+narrateur|Amir souffle, tout doucement.
+narrateur|Le cacao sent encore, tout chaud.
+enfant-m|Bravo papa.
+papa|Merci, Amir. Tu as dit bravo.
 papa|On peut rejouer plus tard.
-narrateur|Kenzo hoche la tête. Il va boire de l'eau. Le nœud se desserre. Perdre, c'est le jeu. On peut être déçu. On dit bravo. On rejoue plus tard.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-m|Plus tard ?
+papa|Oui. D'abord on range un peu.
+narrateur|Amir glisse une carte dans la boîte.
+narrateur|Le carton fait un petit bruit.
+papa|Tu as fini de ranger cette carte ?
+enfant-m|Oui. J'ai encore le nœud.
+papa|C'est permis. On va boire le cacao.
+narrateur|Amir boit une gorgée. C'est doux.
+narrateur|Le nœud se desserre un peu.
+papa|Perdre, c'est le jeu.
+papa|On peut être déçu. On dit bravo.
+papa|On rejoue plus tard.
+enfant-m|On rejoue plus tard.
+narrateur|La pendule fait encore tic.
+narrateur|Le rond de vapeur s'efface doucement.
+papa|Tu as dit bravo, Amir.
+papa|Bravo. Tu as fait du bon travail.
+enfant-m|L'autre peut gagner.
+papa|Oui. Et c'est permis d'être déçu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1348,7 +1395,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Papa a gagné. Que peut faire Kenzo ?</t>
+          <t>Papa a gagné. Que peut faire Amir ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,10 +1551,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Papa a gagné. Que peut faire Kenzo ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Papa a gagné.
+narrateur|Que peut faire Amir ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,7 +1579,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a dit bravo. Il était déçu, et c'était permis. Ils rejoueront plus tard.</t>
+          <t>Amir a dit bravo. Il était déçu, et c'était permis. On rejoue plus tard, d'accord ? D'accord, papa. Bravo. L'autre peut gagner. C'est le jeu. Amir pose la main sur la boîte. Le bois est lisse et tiède.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,10 +1723,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a dit bravo. Il était déçu, et c'était permis. Ils rejoueront plus tard.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Amir a dit bravo.
+narrateur|Il était déçu, et c'était permis.
+papa|On rejoue plus tard, d'accord ?
+enfant-m|D'accord, papa.
+papa|Bravo. L'autre peut gagner. C'est le jeu.
+narrateur|Amir pose la main sur la boîte.
+narrateur|Le bois est lisse et tiède.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,7 +1756,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Kenzo range la boîte. Papa range la nappe. Ils vont lire un livre.</t>
+          <t>On range la boîte ? Oui, papa. Amir range la boîte dans le tiroir. Papa plie la nappe, tout doucement. On va lire un livre ? Oui. Un petit livre. Le cacao n'a plus de vapeur. Plus tard, on rejoue.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,10 +1892,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo range la boîte. Papa range la nappe. Ils vont lire un livre.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>papa|On range la boîte ?
+enfant-m|Oui, papa.
+narrateur|Amir range la boîte dans le tiroir.
+narrateur|Papa plie la nappe, tout doucement.
+papa|On va lire un livre ?
+enfant-m|Oui. Un petit livre.
+narrateur|Le cacao n'a plus de vapeur.
+papa|Plus tard, on rejoue.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1868,7 +1926,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le livre est ouvert sur les genoux. J'étais déçu. C'était permis. Oui. Tu as dit bravo. On rejoue plus tard. Bravo, Amir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,10 +2066,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le livre est ouvert sur les genoux.
+enfant-m|J'étais déçu. C'était permis.
+papa|Oui. Tu as dit bravo.
+papa|On rejoue plus tard.
+papa|Bravo, Amir.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2130,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.001-01.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.001-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La pendule de bois fait tic, tout doux. Un peu de vapeur monte du cacao. Elle laisse un rond sur la vitre. La nappe à carreaux est un peu rêche. Une boîte de cartes dépasse du tiroir. Tu as vu le rond sur la vitre, Amir ? Oui, papa. C'est chaud. En ce moment, papa ouvre la boîte. Les cartes sont lisses et un peu froides. Amir les pose sur la nappe, une par une. Elles sentent le bois. Oui. On joue un petit tour. Amir a envie de gagner. Il regarde ses cartes, tout près. Papa pose sa dernière carte. J'ai fini. J'ai gagné ce tour. Amir sent un nœud dans le ventre. Ses yeux piquent un peu. Je suis déçu. Être déçu, c'est permis. L'autre peut gagner. C'est le jeu. Amir souffle, tout doucement. Le cacao sent encore, tout chaud. Bravo papa. Merci, Amir. Tu as dit bravo. On peut rejouer plus tard. Plus tard ? Oui. D'abord on range un peu. Amir glisse une carte dans la boîte. Le carton fait un petit bruit. Tu as fini de ranger cette carte ? Oui. J'ai encore le nœud. C'est permis. On va boire le cacao. Amir boit une gorgée. C'est doux. Le nœud se desserre un peu. Perdre, c'est le jeu. On peut être déçu. On dit bravo. On rejoue plus tard. On rejoue plus tard. La pendule fait encore tic. Le rond de vapeur s'efface doucement. Tu as dit bravo, Amir. Bravo. Tu as fait du bon travail. L'autre peut gagner. Oui. Et c'est permis d'être déçu.</t>
+          <t>La pendule de bois fait tic, tout doux. Un peu de vapeur monte du cacao. Elle laisse un rond sur la vitre. La nappe à carreaux est un peu rêche. Une boîte de cartes dépasse du tiroir. Tu as vu le rond sur la vitre, Amir ? Oui, papa. C'est chaud. En ce moment, papa ouvre la boîte. Les cartes sont lisses et un peu froides. Amir les pose sur la nappe, une par une. Elles sentent le bois. Oui. On joue un petit tour. Amir a envie de gagner. Il regarde ses cartes, tout près. Papa pose sa dernière carte. J'ai fini. J'ai gagné ce tour. Amir sent un nœud dans le ventre. Ses yeux piquent un peu. Je suis déçu. Être déçu, c'est permis. L'autre peut gagner. C'est le jeu. Amir souffle, tout doucement. Le cacao sent encore, tout chaud. Bravo papa. Merci, Amir. Tu as dit bravo. On peut rejouer plus tard. Plus tard ? Oui. D'abord on range un peu. Amir glisse une carte dans la boîte. Le carton fait un petit bruit. Tu as fini de ranger cette carte ? Oui. J'ai encore le nœud. C'est permis. On va boire le cacao. Amir boit une gorgée. C'est doux. Le nœud se desserre un peu. Perdre, c'est le jeu. On peut être déçu. On dit bravo. On rejoue plus tard. On rejoue plus tard. La pendule fait encore tic. Le rond de vapeur s'efface doucement. Tu as dit bravo, Amir. L'autre peut gagner. Oui. Et c'est permis d'être déçu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Kenzo et papa jouent aux cartes, à la table. Les cartes sont lisses. Kenzo a envie de gagner. Papa pose sa dernière carte. Papa a gagné. Kenzo sent un nœud dans le ventre. Ses yeux piquent un peu. Papa dit : &lt;emphasis level="moderate"&gt;l'autre&lt;/emphasis&gt; peut gagner. C'est le jeu. Kenzo dit : je suis déçu. Papa dit : être déçu, c'est permis. Kenzo souffle. Il dit : bravo papa. Papa sourit. Kenzo range une carte. Papa dit : on peut rejouer plus tard. Kenzo hoche la tête. Il va boire de l'eau. Le nœud se desserre. Perdre, c'est le jeu. On peut être déçu. On dit bravo. On rejoue plus tard.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La pendule de bois fait tic, tout doux. Un peu de vapeur monte du cacao. Elle laisse un rond sur la vitre. La nappe à carreaux est un peu rêche. Une boîte de cartes dépasse du tiroir. Tu as vu le rond sur la vitre, Amir ? Oui, papa. C'est chaud. En ce moment, papa ouvre la boîte. Les cartes sont lisses et un peu froides. Amir les pose sur la nappe, une par une. Elles sentent le bois. Oui. On joue un petit tour. Amir a envie de gagner. Il regarde ses cartes, tout près. Papa pose sa dernière carte. J'ai fini. J'ai gagné ce tour. Amir sent un nœud dans le ventre. Ses yeux piquent un peu. Je suis déçu. Être déçu, c'est permis. L'autre peut gagner. C'est le jeu. Amir souffle, tout doucement. Le cacao sent encore, tout chaud. Bravo papa. Merci, Amir. Tu as dit bravo. On peut rejouer plus tard. Plus tard ? Oui. D'abord on range un peu. Amir glisse une carte dans la boîte. Le carton fait un petit bruit. Tu as fini de ranger cette carte ? Oui. J'ai encore le nœud. C'est permis. On va boire le cacao. Amir boit une gorgée. C'est doux. Le nœud se desserre un peu. Perdre, c'est le jeu. On peut être déçu. On dit bravo. On rejoue plus tard. On rejoue plus tard. La pendule fait encore tic. Le rond de vapeur s'efface doucement. Tu as dit bravo, Amir. L'autre peut gagner. Oui. Et c'est permis d'être déçu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1366,7 +1366,6 @@
 narrateur|La pendule fait encore tic.
 narrateur|Le rond de vapeur s'efface doucement.
 papa|Tu as dit bravo, Amir.
-papa|Bravo. Tu as fait du bon travail.
 enfant-m|L'autre peut gagner.
 papa|Oui. Et c'est permis d'être déçu.</t>
         </is>
@@ -1400,7 +1399,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Papa a gagné. Que peut faire Kenzo ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa a gagné. Que peut faire Amir ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1584,7 +1583,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Kenzo a dit bravo. Il était &lt;emphasis level="moderate"&gt;déçu&lt;/emphasis&gt;, et c'était permis. Ils rejoueront plus tard.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a dit bravo. Il était déçu, et c'était permis. On rejoue plus tard, d'accord ? D'accord, papa. Bravo. L'autre peut gagner. C'est le jeu. Amir pose la main sur la boîte. Le bois est lisse et tiède.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1761,7 +1760,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Kenzo range la boîte. Papa range la nappe. Ils vont lire un livre.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On range la boîte ? Oui, papa. Amir range la boîte dans le tiroir. Papa plie la nappe, tout doucement. On va lire un livre ? Oui. Un petit livre. Le cacao n'a plus de vapeur. Plus tard, on rejoue.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1926,12 +1925,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le livre est ouvert sur les genoux. J'étais déçu. C'était permis. Oui. Tu as dit bravo. On rejoue plus tard. Bravo, Amir. L'histoire est finie.</t>
+          <t>Le livre est ouvert sur les genoux. J'étais déçu. C'était permis. Oui. Tu as dit bravo. On rejoue plus tard. Bravo, Amir.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le livre est ouvert sur les genoux. J'étais déçu. C'était permis. Oui. Tu as dit bravo. On rejoue plus tard. Bravo, Amir.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2070,8 +2069,7 @@
 enfant-m|J'étais déçu. C'était permis.
 papa|Oui. Tu as dit bravo.
 papa|On rejoue plus tard.
-papa|Bravo, Amir.
-narrateur|L'histoire est finie.</t>
+papa|Bravo, Amir.</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2137,6 +2135,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.001-01.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.001-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maison</t>
+          <t>maison, table sous la pendule</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kenzo, papa</t>
+          <t>Amir, papa</t>
         </is>
       </c>
     </row>
